--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>137193916</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137193917</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>137193918</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137193919</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137193920</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>137193916</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>137193917</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>137193918</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137193919</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>137193920</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -845,11 +841,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -975,11 +967,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1245,11 +1233,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1380,11 +1364,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1520,11 +1500,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1660,11 +1636,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1800,11 +1772,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137193916</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>137193917</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137193918</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>137193919</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137193920</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137193916</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>137193917</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137193918</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>137193919</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137193920</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>137193916</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>137193917</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137193918</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>137193919</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>137193920</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 40327-2026 artfynd.xlsx
+++ b/artfynd/A 40327-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193967</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193970</v>
       </c>
       <c r="B3" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>137193910</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>137193971</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
